--- a/result/趋势_vs_强势.xlsx
+++ b/result/趋势_vs_强势.xlsx
@@ -480,22 +480,22 @@
         <v>337</v>
       </c>
       <c r="C2" t="n">
-        <v>4.09</v>
+        <v>4.01</v>
       </c>
       <c r="D2" t="n">
         <v>24.07</v>
       </c>
       <c r="E2" t="n">
-        <v>-59.35</v>
+        <v>-59.08</v>
       </c>
       <c r="F2" t="n">
-        <v>1379388.41</v>
+        <v>1352217.9</v>
       </c>
       <c r="G2" t="n">
-        <v>31.43</v>
+        <v>31.52</v>
       </c>
       <c r="H2" t="n">
-        <v>91.39</v>
+        <v>91.69</v>
       </c>
     </row>
     <row r="3">

--- a/result/趋势_vs_强势.xlsx
+++ b/result/趋势_vs_强势.xlsx
@@ -508,7 +508,7 @@
         <v>235</v>
       </c>
       <c r="C3" t="n">
-        <v>3.75</v>
+        <v>5.88</v>
       </c>
       <c r="D3" t="n">
         <v>196.3</v>
@@ -517,13 +517,13 @@
         <v>-19.77</v>
       </c>
       <c r="F3" t="n">
-        <v>882304.6899999999</v>
+        <v>1381991.17</v>
       </c>
       <c r="G3" t="n">
-        <v>6.31</v>
+        <v>13.3</v>
       </c>
       <c r="H3" t="n">
-        <v>41.7</v>
+        <v>42.55</v>
       </c>
     </row>
   </sheetData>

--- a/result/趋势_vs_强势.xlsx
+++ b/result/趋势_vs_强势.xlsx
@@ -480,19 +480,19 @@
         <v>337</v>
       </c>
       <c r="C2" t="n">
-        <v>4.01</v>
+        <v>3.95</v>
       </c>
       <c r="D2" t="n">
         <v>24.07</v>
       </c>
       <c r="E2" t="n">
-        <v>-59.08</v>
+        <v>-61.2</v>
       </c>
       <c r="F2" t="n">
-        <v>1352217.9</v>
+        <v>1331993.22</v>
       </c>
       <c r="G2" t="n">
-        <v>31.52</v>
+        <v>31.61</v>
       </c>
       <c r="H2" t="n">
         <v>91.69</v>

--- a/result/趋势_vs_强势.xlsx
+++ b/result/趋势_vs_强势.xlsx
@@ -477,25 +477,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="C2" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="D2" t="n">
         <v>24.07</v>
       </c>
       <c r="E2" t="n">
-        <v>-61.2</v>
+        <v>-62.26</v>
       </c>
       <c r="F2" t="n">
-        <v>1331993.22</v>
+        <v>1338889.43</v>
       </c>
       <c r="G2" t="n">
-        <v>31.61</v>
+        <v>30.75</v>
       </c>
       <c r="H2" t="n">
-        <v>91.69</v>
+        <v>91.48</v>
       </c>
     </row>
     <row r="3">
@@ -505,10 +505,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C3" t="n">
-        <v>5.88</v>
+        <v>5.93</v>
       </c>
       <c r="D3" t="n">
         <v>196.3</v>
@@ -517,13 +517,13 @@
         <v>-19.77</v>
       </c>
       <c r="F3" t="n">
-        <v>1381991.17</v>
+        <v>1422456.83</v>
       </c>
       <c r="G3" t="n">
-        <v>13.3</v>
+        <v>13.19</v>
       </c>
       <c r="H3" t="n">
-        <v>42.55</v>
+        <v>43.33</v>
       </c>
     </row>
   </sheetData>

--- a/result/趋势_vs_强势.xlsx
+++ b/result/趋势_vs_强势.xlsx
@@ -477,10 +477,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>352</v>
+        <v>380</v>
       </c>
       <c r="C2" t="n">
-        <v>3.8</v>
+        <v>3.51</v>
       </c>
       <c r="D2" t="n">
         <v>24.07</v>
@@ -489,13 +489,13 @@
         <v>-62.26</v>
       </c>
       <c r="F2" t="n">
-        <v>1338889.43</v>
+        <v>1331993.55</v>
       </c>
       <c r="G2" t="n">
-        <v>30.75</v>
+        <v>29.46</v>
       </c>
       <c r="H2" t="n">
-        <v>91.48</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3">
@@ -505,25 +505,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C3" t="n">
-        <v>5.93</v>
+        <v>5.4</v>
       </c>
       <c r="D3" t="n">
         <v>196.3</v>
       </c>
       <c r="E3" t="n">
-        <v>-19.77</v>
+        <v>-28.63</v>
       </c>
       <c r="F3" t="n">
-        <v>1422456.83</v>
+        <v>1339649.88</v>
       </c>
       <c r="G3" t="n">
-        <v>13.19</v>
+        <v>13.17</v>
       </c>
       <c r="H3" t="n">
-        <v>43.33</v>
+        <v>42.34</v>
       </c>
     </row>
   </sheetData>
